--- a/artfynd/A 3395-2023 artfynd.xlsx
+++ b/artfynd/A 3395-2023 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Melina Eberhagen</t>
+          <t>Via Melina Eberhagen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 3395-2023 artfynd.xlsx
+++ b/artfynd/A 3395-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123156514</v>
       </c>
       <c r="B2" t="n">
-        <v>109041</v>
+        <v>109045</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 3395-2023 artfynd.xlsx
+++ b/artfynd/A 3395-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123156514</v>
       </c>
       <c r="B2" t="n">
-        <v>109045</v>
+        <v>109047</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 3395-2023 artfynd.xlsx
+++ b/artfynd/A 3395-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123156514</v>
       </c>
       <c r="B2" t="n">
-        <v>109047</v>
+        <v>109053</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 3395-2023 artfynd.xlsx
+++ b/artfynd/A 3395-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123156514</v>
       </c>
       <c r="B2" t="n">
-        <v>109053</v>
+        <v>109056</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 3395-2023 artfynd.xlsx
+++ b/artfynd/A 3395-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123156514</v>
       </c>
       <c r="B2" t="n">
-        <v>109056</v>
+        <v>109073</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 3395-2023 artfynd.xlsx
+++ b/artfynd/A 3395-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123156514</v>
       </c>
       <c r="B2" t="n">
-        <v>109073</v>
+        <v>109091</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 3395-2023 artfynd.xlsx
+++ b/artfynd/A 3395-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123156514</v>
       </c>
       <c r="B2" t="n">
-        <v>109091</v>
+        <v>109093</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 3395-2023 artfynd.xlsx
+++ b/artfynd/A 3395-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123156514</v>
       </c>
       <c r="B2" t="n">
-        <v>109093</v>
+        <v>108668</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 3395-2023 artfynd.xlsx
+++ b/artfynd/A 3395-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,116 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128327839</v>
+      </c>
+      <c r="B3" t="n">
+        <v>109088</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220228</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sommarfibbla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Leontodon hispidus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Artrik vägkant, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>522930</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6458587</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Gammalkil</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>SödraInneslänt (IS)Julia Svensson</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 3395-2023 artfynd.xlsx
+++ b/artfynd/A 3395-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128327839</v>
       </c>
       <c r="B3" t="n">
-        <v>109088</v>
+        <v>109093</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3395-2023 artfynd.xlsx
+++ b/artfynd/A 3395-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128327839</v>
       </c>
       <c r="B3" t="n">
-        <v>109093</v>
+        <v>109186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3395-2023 artfynd.xlsx
+++ b/artfynd/A 3395-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128327839</v>
       </c>
       <c r="B3" t="n">
-        <v>109186</v>
+        <v>109210</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3395-2023 artfynd.xlsx
+++ b/artfynd/A 3395-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128327839</v>
       </c>
       <c r="B3" t="n">
-        <v>109210</v>
+        <v>109223</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3395-2023 artfynd.xlsx
+++ b/artfynd/A 3395-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128327839</v>
       </c>
       <c r="B3" t="n">
-        <v>109223</v>
+        <v>109232</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3395-2023 artfynd.xlsx
+++ b/artfynd/A 3395-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128327839</v>
       </c>
       <c r="B3" t="n">
-        <v>109232</v>
+        <v>109237</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3395-2023 artfynd.xlsx
+++ b/artfynd/A 3395-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128327839</v>
       </c>
       <c r="B3" t="n">
-        <v>109237</v>
+        <v>109265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3395-2023 artfynd.xlsx
+++ b/artfynd/A 3395-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128327839</v>
       </c>
       <c r="B3" t="n">
-        <v>109265</v>
+        <v>109278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3395-2023 artfynd.xlsx
+++ b/artfynd/A 3395-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128327839</v>
       </c>
       <c r="B3" t="n">
-        <v>109278</v>
+        <v>109282</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3395-2023 artfynd.xlsx
+++ b/artfynd/A 3395-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123156514</v>
+        <v>123156495</v>
       </c>
       <c r="B2" t="n">
-        <v>108668</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109866</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,17 +703,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sandlyckan, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522931</v>
+        <v>522918</v>
       </c>
       <c r="R2" t="n">
-        <v>6458588</v>
+        <v>6458595</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +759,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Södra vägsidan, innerslänt</t>
+          <t>Norra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128327839</v>
+        <v>123156513</v>
       </c>
       <c r="B3" t="n">
-        <v>109282</v>
+        <v>109866</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,17 +825,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Artrik vägkant, Ög</t>
+          <t>Sandlyckan, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522930</v>
+        <v>522914</v>
       </c>
       <c r="R3" t="n">
-        <v>6458587</v>
+        <v>6458584</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,7 +869,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>SödraInneslänt (IS)Julia Svensson</t>
+          <t>Södra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,15 +884,986 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Via Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123156514</v>
+      </c>
+      <c r="B4" t="n">
+        <v>109866</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220228</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sommarfibbla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Leontodon hispidus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sandlyckan, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>522931</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6458588</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gammalkil</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Södra vägsidan, innerslänt</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123178370</v>
+      </c>
+      <c r="B5" t="n">
+        <v>109866</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220228</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sommarfibbla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Leontodon hispidus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sandlyckan, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>522903</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6458578</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gammalkil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Södra vägsidan, innerslänt</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128327839</v>
+      </c>
+      <c r="B6" t="n">
+        <v>109866</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220228</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sommarfibbla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leontodon hispidus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Artrik vägkant, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>522930</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6458587</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gammalkil</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>SödraInneslänt (IS)Julia Svensson</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Magnus Stenmark</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Magnus Stenmark</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>101190108</v>
+      </c>
+      <c r="B7" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Duseborg, Gammalkil, Linköpings kommun, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>522924</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6458514</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gammalkil</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-05-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-05-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Felicia Skorsdal</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Felicia Skorsdal</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123156512</v>
+      </c>
+      <c r="B8" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sandlyckan, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>522910</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6458583</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gammalkil</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Södra vägsidan, innerslänt</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123178351</v>
+      </c>
+      <c r="B9" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sandlyckan, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>522894</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6458585</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gammalkil</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Norra vägsidan, hela vägområdet</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123156494</v>
+      </c>
+      <c r="B10" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sandlyckan, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>522932</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6458602</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gammalkil</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Norra vägsidan, innerslänt</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123156492</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99754</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222295</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sandlyckan, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>522913</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6458592</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gammalkil</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Norra vägsidan, ytterslänt</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123178368</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sandlyckan, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>522885</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6458570</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gammalkil</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Södra vägsidan, innerslänt</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 3395-2023 artfynd.xlsx
+++ b/artfynd/A 3395-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123156495</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123156513</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123156514</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123178370</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,6 +1244,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128327839</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1316,6 +1346,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101190108</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123156512</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1537,6 +1577,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123178351</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1647,6 +1692,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123156494</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1762,6 +1812,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123156492</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1868,8 +1923,26 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123178368</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>